--- a/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -586,8 +586,8 @@
   <x:dimension ref="A1:B6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="88.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="35.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="88.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="35.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">

--- a/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -587,7 +587,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="88.139196" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="35.424911" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="35.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
